--- a/IdrissaKoakon.com/projets/Copie de 6- Annexe 6-1 - Tableau de synthèse - Epreuve E4 - BTS SIO 20231.xlsx
+++ b/IdrissaKoakon.com/projets/Copie de 6- Annexe 6-1 - Tableau de synthèse - Epreuve E4 - BTS SIO 20231.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mimou\Desktop\portfolio\.fr-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mimou\Desktop\BTS\Projets\E5 (portfolio)\porfololio v2\IdrissaKoakon.com\projets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{947A87BE-9C6D-436C-9A0B-88A8F4B5D5C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA169B11-7035-464A-8913-70806DD9B3A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="46">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
-  </si>
-  <si>
-    <t>SESSION 2023</t>
   </si>
   <si>
     <t xml:space="preserve">Tableau de synthèse des réalisations professionnelles </t>
@@ -155,40 +152,10 @@
 oeuvre de solution d'hébergement et cloud</t>
   </si>
   <si>
-    <t>Déploiement d'agents sur les machines du parc (agents GLPI)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIO2 - Réalisation d'un portfolio avec le CMS Wordpress (création d'article, référencement SEO).
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">réalisation d’un Site Web «  Gestion d’un Zoo (HTML , CSS, JS ET PHP) Le fichier SQL de la base de données Les maquettes   ( figma )
-</t>
-  </si>
-  <si>
-    <t>Installation et configuration gestionnaire de parc et d'incident (GLPI)</t>
-  </si>
-  <si>
-    <t>Mise en place d'une infrastructure réseau virtuelle (Cisco Packet Tracer)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mettre en place une formation de cyberdéfense </t>
-  </si>
-  <si>
-    <t>Mise en place d'une infrastructure complète pour des utilisateurs DHCP, DNS, Active Directory(Windows serveur 2012)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mise en place d'une infrastructure système complète (environnement Linux) Langage de commende power shell, manipulation des fichiers, gestion des droits </t>
-  </si>
-  <si>
     <t>Réalisations en milieu professionnel en cours de première année</t>
   </si>
   <si>
     <t>Réalisations en milieu professionnel en cours de seconde année</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support et Formation: assistance, conseil et formation aux utilisateurs sur les outils bureautiques et téléphoniques.
-</t>
   </si>
   <si>
     <t>Gestion des incidents: Prendre en charge les incidents techniques conjointement avec le Service Desk.
@@ -196,10 +163,6 @@
   </si>
   <si>
     <t>Onbaording de nouveau poste pour les nouveaux utilisateur.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gestion des Équipements : Assurer la mise à disposition et la restitution des matériels lors des arrivées et départs des collaborateurs.
-</t>
   </si>
   <si>
     <t>Prepartion des commandes des nouveaux postes, mobiles et accessoires .</t>
@@ -214,6 +177,47 @@
   <si>
     <t>Rédigé des guides et formé les utilisateurs.</t>
   </si>
+  <si>
+    <t>11/112024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIO 1 - semestre 1 - Réalisation d'un portfolio avec le CMS Wordpress (création d'article, référencement SEO).
+</t>
+  </si>
+  <si>
+    <t>SIO 1 - semestre 1 - Déploiement d'agents sur les machines du parc (agents GLPI)</t>
+  </si>
+  <si>
+    <t>Gestion des Équipements : Assurer la mise à disposition et la restitution des matériels lors des arrivées et départs des collaborateurs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIO 1 - semestre 1 - Mettre en place une formation de cyberdéfense </t>
+  </si>
+  <si>
+    <t>SESSION 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIO 1 - semestre 2 - réalisation d’un Site Web «  Gestion d’un Zoo (HTML , CSS, JS ET PHP) Le fichier SQL de la base de données Les maquettes   ( figma )
+</t>
+  </si>
+  <si>
+    <t>SIO 1 - semestre 2 - Installation et configuration gestionnaire de parc et d'incident (GLPI)</t>
+  </si>
+  <si>
+    <t>SIO 1 - semestre 2 - Mise en place d'une infrastructure réseau virtuelle (Cisco Packet Tracer)</t>
+  </si>
+  <si>
+    <t>SIO 1 - semestre 2 -Gestion d'un stockage externe redondant dans un réseau avec les RAID (TrueNas)</t>
+  </si>
+  <si>
+    <t>SIO 2 - semestre 2 - Mise en place d'une infrastructure complète pour des utilisateurs DHCP, DNS, Active Directory(Windows serveur 2012)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SIO 2 - semestre 1 - Mise en place d'une infrastructure système complète (environnement Linux) Langage de commende power shell, manipulation des fichiers, gestion des droits </t>
+  </si>
+  <si>
+    <t>SIO 2 - semestre 2 - Installation et configuration d'ESXi pour la virtualisation de machines virtuelles</t>
+  </si>
 </sst>
 </file>
 
@@ -222,7 +226,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -312,13 +316,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -326,7 +323,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -351,8 +348,14 @@
         <bgColor rgb="FF00FFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="28">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -674,56 +677,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF494429"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF494429"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF494429"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF494429"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF494429"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF494429"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF494429"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF494429"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF494429"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -773,21 +731,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -802,6 +745,15 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -841,13 +793,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1073,151 +1019,151 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M1000"/>
+  <dimension ref="A1:M995"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="70.42578125" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="8" width="18.7109375" customWidth="1"/>
     <col min="9" max="28" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="33" t="s">
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1" s="32"/>
+    </row>
+    <row r="2" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="34"/>
-    </row>
-    <row r="2" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="33" t="s">
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+    </row>
+    <row r="3" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-    </row>
-    <row r="3" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="35" t="s">
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="38" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="36"/>
-      <c r="H3" s="39"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="37"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="4" t="s">
+    </row>
+    <row r="5" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="28" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="30" t="s">
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="30"/>
+    </row>
+    <row r="6" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="31"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="32"/>
-    </row>
-    <row r="6" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="40" t="s">
+      <c r="B6" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="C6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="F6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="G6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="H6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="6" t="s">
+    </row>
+    <row r="7" spans="1:13" ht="309.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="39"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="7" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="324.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="41"/>
-      <c r="B7" s="43"/>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="E7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="F7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="G7" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="H7" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H7" s="8" t="s">
+    </row>
+    <row r="8" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="42" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="44" t="s">
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="37"/>
+    </row>
+    <row r="9" spans="1:13" ht="30" x14ac:dyDescent="0.2">
+      <c r="A9" s="9" t="s">
         <v>24</v>
-      </c>
-      <c r="B8" s="36"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="39"/>
-    </row>
-    <row r="9" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="9" t="s">
-        <v>25</v>
       </c>
       <c r="B9" s="10">
         <v>45209</v>
@@ -1229,9 +1175,9 @@
       <c r="G9" s="13"/>
       <c r="H9" s="14"/>
     </row>
-    <row r="10" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B10" s="10">
         <v>45245</v>
@@ -1243,9 +1189,9 @@
       <c r="G10" s="13"/>
       <c r="H10" s="14"/>
     </row>
-    <row r="11" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" ht="45" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B11" s="15">
         <v>45391</v>
@@ -1257,9 +1203,9 @@
       <c r="G11" s="12"/>
       <c r="H11" s="14"/>
     </row>
-    <row r="12" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" ht="60" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="B12" s="15">
         <v>45377</v>
@@ -1273,7 +1219,7 @@
     </row>
     <row r="13" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B13" s="15">
         <v>45395</v>
@@ -1287,7 +1233,7 @@
     </row>
     <row r="14" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B14" s="15">
         <v>45329</v>
@@ -1299,19 +1245,23 @@
       <c r="G14" s="13"/>
       <c r="H14" s="16"/>
     </row>
-    <row r="15" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="9"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="49"/>
+    <row r="15" spans="1:13" ht="30" x14ac:dyDescent="0.2">
+      <c r="A15" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="15">
+        <v>45306</v>
+      </c>
+      <c r="C15" s="13"/>
       <c r="D15" s="12"/>
       <c r="E15" s="12"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="49"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
       <c r="H15" s="16"/>
     </row>
     <row r="16" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B16" s="15">
         <v>45417</v>
@@ -1323,221 +1273,242 @@
       <c r="G16" s="13"/>
       <c r="H16" s="14"/>
     </row>
-    <row r="17" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" ht="45" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="15">
+        <v>45537</v>
+      </c>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="16"/>
+    </row>
+    <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.2">
+      <c r="A18" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="15">
+        <v>45777</v>
+      </c>
+      <c r="C18" s="20"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="16"/>
+    </row>
+    <row r="19" spans="1:8" ht="45" x14ac:dyDescent="0.2">
+      <c r="A19" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="15">
+        <v>45679</v>
+      </c>
+      <c r="C19" s="13"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="16"/>
+    </row>
+    <row r="20" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="26"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="44"/>
+    </row>
+    <row r="21" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="15">
+        <v>45493</v>
+      </c>
+      <c r="C21" s="12"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="21"/>
+    </row>
+    <row r="22" spans="1:8" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="15">
+        <v>45461</v>
+      </c>
+      <c r="C22" s="12"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="21"/>
+    </row>
+    <row r="23" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="15">
-        <v>45365</v>
+      <c r="B23" s="15">
+        <v>45461</v>
       </c>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="16"/>
-    </row>
-    <row r="18" spans="1:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" s="15">
-        <v>45353</v>
-      </c>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="16"/>
-    </row>
-    <row r="19" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="45" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="46"/>
-    </row>
-    <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="17"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="26"/>
-    </row>
-    <row r="21" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="47"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="16"/>
-    </row>
-    <row r="22" spans="1:8" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="17"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="26"/>
-    </row>
-    <row r="23" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="48" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23" s="17"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
       <c r="E23" s="12"/>
       <c r="F23" s="12"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="26"/>
-    </row>
-    <row r="24" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="9"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="16"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="21"/>
+    </row>
+    <row r="24" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="26"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="44"/>
     </row>
     <row r="25" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="9"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="12"/>
+      <c r="A25" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="20"/>
       <c r="D25" s="12"/>
       <c r="E25" s="12"/>
       <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
+      <c r="G25" s="20"/>
       <c r="H25" s="16"/>
     </row>
-    <row r="26" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="9"/>
-      <c r="B26" s="17"/>
+    <row r="26" spans="1:8" ht="45" x14ac:dyDescent="0.2">
+      <c r="A26" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="15">
+        <v>45609</v>
+      </c>
       <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
+      <c r="D26" s="20"/>
       <c r="E26" s="12"/>
       <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="16"/>
-    </row>
-    <row r="27" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="45" t="s">
-        <v>35</v>
+      <c r="G26" s="20"/>
+      <c r="H26" s="21"/>
+    </row>
+    <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.2">
+      <c r="A27" s="22" t="s">
+        <v>30</v>
       </c>
-      <c r="B27" s="28"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="46"/>
-    </row>
-    <row r="28" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="9" t="s">
-        <v>38</v>
+      <c r="B27" s="15">
+        <v>45609</v>
       </c>
-      <c r="B28" s="17"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="12"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="21"/>
+    </row>
+    <row r="28" spans="1:8" ht="45" x14ac:dyDescent="0.2">
+      <c r="A28" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" s="15">
+        <v>45612</v>
+      </c>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
       <c r="E28" s="12"/>
       <c r="F28" s="12"/>
-      <c r="G28" s="25"/>
+      <c r="G28" s="20"/>
       <c r="H28" s="16"/>
     </row>
-    <row r="29" spans="1:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="48" t="s">
-        <v>37</v>
+    <row r="29" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="9" t="s">
+        <v>29</v>
       </c>
-      <c r="B29" s="17"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="25"/>
+      <c r="B29" s="15">
+        <v>45612</v>
+      </c>
+      <c r="C29" s="20"/>
+      <c r="D29" s="12"/>
       <c r="E29" s="12"/>
       <c r="F29" s="12"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="26"/>
-    </row>
-    <row r="30" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" s="17"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="25"/>
-      <c r="H30" s="26"/>
-    </row>
-    <row r="31" spans="1:8" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="17"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="16"/>
-    </row>
-    <row r="32" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" s="17"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="25"/>
-      <c r="H32" s="16"/>
-    </row>
-    <row r="33" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="9"/>
-      <c r="B33" s="17"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="16"/>
-    </row>
-    <row r="34" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="18"/>
-      <c r="B34" s="19"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="21"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="16"/>
+    </row>
+    <row r="30" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="17"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+    </row>
+    <row r="31" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+    </row>
+    <row r="32" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+    </row>
+    <row r="33" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+    </row>
+    <row r="34" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
     </row>
     <row r="35" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="22"/>
-      <c r="B35" s="23"/>
-      <c r="C35" s="24"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="24"/>
-      <c r="G35" s="24"/>
-      <c r="H35" s="24"/>
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
     </row>
     <row r="36" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -11139,63 +11110,13 @@
       <c r="G995" s="1"/>
       <c r="H995" s="1"/>
     </row>
-    <row r="996" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A996" s="1"/>
-      <c r="B996" s="1"/>
-      <c r="C996" s="1"/>
-      <c r="D996" s="1"/>
-      <c r="E996" s="1"/>
-      <c r="F996" s="1"/>
-      <c r="G996" s="1"/>
-      <c r="H996" s="1"/>
-    </row>
-    <row r="997" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A997" s="1"/>
-      <c r="B997" s="1"/>
-      <c r="C997" s="1"/>
-      <c r="D997" s="1"/>
-      <c r="E997" s="1"/>
-      <c r="F997" s="1"/>
-      <c r="G997" s="1"/>
-      <c r="H997" s="1"/>
-    </row>
-    <row r="998" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A998" s="1"/>
-      <c r="B998" s="1"/>
-      <c r="C998" s="1"/>
-      <c r="D998" s="1"/>
-      <c r="E998" s="1"/>
-      <c r="F998" s="1"/>
-      <c r="G998" s="1"/>
-      <c r="H998" s="1"/>
-    </row>
-    <row r="999" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A999" s="1"/>
-      <c r="B999" s="1"/>
-      <c r="C999" s="1"/>
-      <c r="D999" s="1"/>
-      <c r="E999" s="1"/>
-      <c r="F999" s="1"/>
-      <c r="G999" s="1"/>
-      <c r="H999" s="1"/>
-    </row>
-    <row r="1000" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1000" s="1"/>
-      <c r="B1000" s="1"/>
-      <c r="C1000" s="1"/>
-      <c r="D1000" s="1"/>
-      <c r="E1000" s="1"/>
-      <c r="F1000" s="1"/>
-      <c r="G1000" s="1"/>
-      <c r="H1000" s="1"/>
-    </row>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A24:H24"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A1:F1"/>
